--- a/marketing_report/outputs/Posgrados/Reporte_Asesores/17_reporte_asesores.xlsx
+++ b/marketing_report/outputs/Posgrados/Reporte_Asesores/17_reporte_asesores.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,6 +443,256 @@
         <is>
           <t>Total_Inscriptos</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Contact Center</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aldana Micaela Quinteros</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>UCASAL Prod</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carla Azcárate</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Fernanda Victoria Meza</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Neuquén Sede_30 NEUQUÉN</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Francisco Gerardo Jover</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>VERONICA PACHTMAN</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Camila Lamas Cil</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ana Sofía Gomez</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Fiamma Alejandra Spring</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Florencia María Rosa Villarreal</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FORMOSA Sede_195</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Aldana Rocio Bruno Blanco</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gabriel Cortes</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Gabriela Cristina Aro Carrizo</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Jorge Ariel Cabaña</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Julieta María García</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Macarena De Singlau</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Melina Salvatierra</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Carolina Eugenia Ferrer</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Paula Luciana Martinez Rosas</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Santiago del Estero Sede_139</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Fátima de los Ángeles Salvatierra Lopez</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -488,7 +738,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
@@ -503,7 +753,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -518,7 +768,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">
@@ -563,7 +813,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -578,7 +828,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -608,7 +858,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -994,10 +1244,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C2" t="n">
-        <v>91.69230769230769</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3">
@@ -1007,10 +1257,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>7.384615384615385</v>
+        <v>7.076923076923077</v>
       </c>
     </row>
     <row r="4">
@@ -1064,10 +1314,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="C2" t="n">
-        <v>43.25842696629213</v>
+        <v>41.72661870503597</v>
       </c>
     </row>
     <row r="3">
@@ -1077,10 +1327,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="C3" t="n">
-        <v>36.51685393258427</v>
+        <v>33.09352517985612</v>
       </c>
     </row>
     <row r="4">
@@ -1090,10 +1340,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>14.04494382022472</v>
+        <v>17.26618705035971</v>
       </c>
     </row>
     <row r="5">
@@ -1106,7 +1356,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>6.179775280898876</v>
+        <v>7.913669064748201</v>
       </c>
     </row>
   </sheetData>
